--- a/download_playwright/exc_data/天猫商品对照表.xlsx
+++ b/download_playwright/exc_data/天猫商品对照表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\my-playwright-project\download_playwright\exc_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03E142D-F51D-461C-9C59-C779071A3EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30C0C05-1721-4C45-9C38-450D984142B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A29DFA99-A10B-4F02-B082-8E919A6452E0}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1900</definedName>
   </definedNames>
-  <calcPr calcId="181029" iterate="1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6753" uniqueCount="3783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6828" uniqueCount="3828">
   <si>
     <t>642523632723</t>
   </si>
@@ -11408,13 +11408,148 @@
   </si>
   <si>
     <t>852010588191</t>
+  </si>
+  <si>
+    <t>868834124642</t>
+  </si>
+  <si>
+    <t>云米super油烟机升级版大吸力大静压顶侧双吸超薄自清洁烟灶联动</t>
+  </si>
+  <si>
+    <t>智能家电</t>
+  </si>
+  <si>
+    <t>860334960361</t>
+  </si>
+  <si>
+    <t>云米顶侧大吸力油烟机燃气灶套装烟灶联动套装5.2KW聚能猛火灶具</t>
+  </si>
+  <si>
+    <t>870799733097</t>
+  </si>
+  <si>
+    <t>云米smart2油烟机 跨界顶侧联动超薄平嵌式自清洁挥手智控大吸力</t>
+  </si>
+  <si>
+    <t>857557599349</t>
+  </si>
+  <si>
+    <t>212115984695</t>
+  </si>
+  <si>
+    <t>云米电烤箱VSO2802台式蒸烤箱一体28L机家用台式蒸汽电烤箱二合一</t>
+  </si>
+  <si>
+    <t>849000374681</t>
+  </si>
+  <si>
+    <t>净水</t>
+  </si>
+  <si>
+    <t>882983410306</t>
+  </si>
+  <si>
+    <t>VIOMI云米新款智能净水器厨房直饮必备反渗透RO六种矿泉七层过滤</t>
+  </si>
+  <si>
+    <t>850883552953</t>
+  </si>
+  <si>
+    <t>VIOMI云米净水器600G小蓝调厨下式RO反渗透直饮家用6年长效</t>
+  </si>
+  <si>
+    <t>857325968546</t>
+  </si>
+  <si>
+    <t>云米前置过滤器家用自来水前置净水器自动反冲洗全屋净水机大流量</t>
+  </si>
+  <si>
+    <t>849648457333</t>
+  </si>
+  <si>
+    <t>873065157674</t>
+  </si>
+  <si>
+    <t>VIOMI云米 滤芯 反渗透滤芯RO膜</t>
+  </si>
+  <si>
+    <t>872941778883</t>
+  </si>
+  <si>
+    <t>VIOMI云米 复合滤芯五合一</t>
+  </si>
+  <si>
+    <t>862873034610</t>
+  </si>
+  <si>
+    <t>新品首发 Viomi云米 小海豚3上市RO净水器5年长效反渗透净水器</t>
+  </si>
+  <si>
+    <t>842195971715</t>
+  </si>
+  <si>
+    <t>VIOMI云米净水器1000G厨下直饮小体积净水机RO机智显龙头3秒满杯</t>
+  </si>
+  <si>
+    <t>852932116812</t>
+  </si>
+  <si>
+    <t>云米净水器600G小海豚升级版厨下式RO反渗透直饮家用</t>
+  </si>
+  <si>
+    <t>852161740747</t>
+  </si>
+  <si>
+    <t>VIOMI云米净水器小海豚600G+升级版厨下式RO反渗透直饮家用</t>
+  </si>
+  <si>
+    <t>846360072018</t>
+  </si>
+  <si>
+    <t>868851073714</t>
+  </si>
+  <si>
+    <t>【新品首发】Viomi云米 小海豚3上市RO净水器5年长效反渗透净水器</t>
+  </si>
+  <si>
+    <t>850333437206</t>
+  </si>
+  <si>
+    <t>VIOMI云米净水器大通量小海豚800G反渗透RO厨下式家用长效滤芯</t>
+  </si>
+  <si>
+    <t>837957770723</t>
+  </si>
+  <si>
+    <t>852614628903</t>
+  </si>
+  <si>
+    <t>850344043841</t>
+  </si>
+  <si>
+    <t>861508688697</t>
+  </si>
+  <si>
+    <t>Viomi云米制冷管线机壁挂式 直饮机 饮水机 UV全水路杀菌速热制冷</t>
+  </si>
+  <si>
+    <t>837301408995</t>
+  </si>
+  <si>
+    <t>VIOMI/云米 新品管线机 冷热管线机Super2 Pro</t>
+  </si>
+  <si>
+    <t>862584688956</t>
+  </si>
+  <si>
+    <t>云米智能门锁CPU门卡感应便携全新防水防折防复制手机APP门卡</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11439,8 +11574,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -11453,8 +11596,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor theme="4" tint="0.39997558519241921"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -11482,13 +11631,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.79998168889431442"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.79998168889431442"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -11511,6 +11671,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -41443,179 +41606,279 @@
       </c>
     </row>
     <row r="1901" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1901" s="2"/>
-      <c r="B1901"/>
-      <c r="C1901"/>
-      <c r="D1901"/>
-      <c r="E1901"/>
+      <c r="A1901" t="s">
+        <v>3783</v>
+      </c>
+      <c r="C1901" t="s">
+        <v>3784</v>
+      </c>
+      <c r="E1901" s="9" t="s">
+        <v>3785</v>
+      </c>
     </row>
     <row r="1902" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1902"/>
-      <c r="B1902"/>
-      <c r="C1902"/>
-      <c r="D1902"/>
-      <c r="E1902"/>
+      <c r="A1902" t="s">
+        <v>3786</v>
+      </c>
+      <c r="C1902" t="s">
+        <v>3787</v>
+      </c>
+      <c r="E1902" s="9" t="s">
+        <v>3785</v>
+      </c>
     </row>
     <row r="1903" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1903"/>
-      <c r="B1903"/>
-      <c r="C1903"/>
-      <c r="D1903"/>
-      <c r="E1903"/>
+      <c r="A1903" t="s">
+        <v>3788</v>
+      </c>
+      <c r="C1903" t="s">
+        <v>3789</v>
+      </c>
+      <c r="E1903" s="9" t="s">
+        <v>3785</v>
+      </c>
     </row>
     <row r="1904" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1904"/>
-      <c r="B1904"/>
-      <c r="C1904"/>
-      <c r="D1904"/>
-      <c r="E1904"/>
+      <c r="A1904" t="s">
+        <v>3790</v>
+      </c>
+      <c r="C1904" t="s">
+        <v>2774</v>
+      </c>
+      <c r="E1904" s="9" t="s">
+        <v>3785</v>
+      </c>
     </row>
     <row r="1905" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1905"/>
-      <c r="B1905"/>
-      <c r="C1905"/>
-      <c r="D1905"/>
-      <c r="E1905"/>
+      <c r="A1905" t="s">
+        <v>3791</v>
+      </c>
+      <c r="C1905" t="s">
+        <v>3792</v>
+      </c>
+      <c r="E1905" s="9" t="s">
+        <v>3785</v>
+      </c>
     </row>
     <row r="1906" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1906"/>
-      <c r="B1906"/>
-      <c r="C1906"/>
-      <c r="D1906"/>
-      <c r="E1906"/>
+      <c r="A1906" t="s">
+        <v>3793</v>
+      </c>
+      <c r="C1906" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E1906" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1907" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1907"/>
-      <c r="B1907"/>
-      <c r="C1907"/>
-      <c r="D1907"/>
-      <c r="E1907"/>
+      <c r="A1907" t="s">
+        <v>3795</v>
+      </c>
+      <c r="C1907" t="s">
+        <v>3796</v>
+      </c>
+      <c r="E1907" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1908" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1908"/>
-      <c r="B1908"/>
-      <c r="C1908"/>
-      <c r="D1908"/>
-      <c r="E1908"/>
+      <c r="A1908" t="s">
+        <v>3797</v>
+      </c>
+      <c r="C1908" t="s">
+        <v>3798</v>
+      </c>
+      <c r="E1908" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1909" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1909"/>
-      <c r="B1909"/>
-      <c r="C1909"/>
-      <c r="D1909"/>
-      <c r="E1909"/>
+      <c r="A1909" t="s">
+        <v>3799</v>
+      </c>
+      <c r="C1909" t="s">
+        <v>3800</v>
+      </c>
+      <c r="E1909" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1910" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1910"/>
-      <c r="B1910"/>
-      <c r="C1910"/>
-      <c r="D1910"/>
-      <c r="E1910"/>
+      <c r="A1910" t="s">
+        <v>3801</v>
+      </c>
+      <c r="C1910" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E1910" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1911" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1911"/>
-      <c r="B1911"/>
-      <c r="C1911"/>
-      <c r="D1911"/>
-      <c r="E1911"/>
+      <c r="A1911" t="s">
+        <v>3802</v>
+      </c>
+      <c r="C1911" t="s">
+        <v>3803</v>
+      </c>
+      <c r="E1911" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1912" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1912"/>
-      <c r="B1912"/>
-      <c r="C1912"/>
-      <c r="D1912"/>
-      <c r="E1912"/>
+      <c r="A1912" t="s">
+        <v>3804</v>
+      </c>
+      <c r="C1912" t="s">
+        <v>3805</v>
+      </c>
+      <c r="E1912" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1913" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1913"/>
-      <c r="B1913"/>
-      <c r="C1913"/>
-      <c r="D1913"/>
-      <c r="E1913"/>
+      <c r="A1913" t="s">
+        <v>3806</v>
+      </c>
+      <c r="C1913" t="s">
+        <v>3807</v>
+      </c>
+      <c r="E1913" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1914" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1914"/>
-      <c r="B1914"/>
-      <c r="C1914"/>
-      <c r="D1914"/>
-      <c r="E1914"/>
+      <c r="A1914" t="s">
+        <v>3808</v>
+      </c>
+      <c r="C1914" t="s">
+        <v>3809</v>
+      </c>
+      <c r="E1914" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1915" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1915"/>
-      <c r="B1915"/>
-      <c r="C1915"/>
-      <c r="D1915"/>
-      <c r="E1915"/>
+      <c r="A1915" t="s">
+        <v>3810</v>
+      </c>
+      <c r="C1915" t="s">
+        <v>3811</v>
+      </c>
+      <c r="E1915" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1916" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1916"/>
-      <c r="B1916"/>
-      <c r="C1916"/>
-      <c r="D1916"/>
-      <c r="E1916"/>
+      <c r="A1916" t="s">
+        <v>3812</v>
+      </c>
+      <c r="C1916" t="s">
+        <v>3813</v>
+      </c>
+      <c r="E1916" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1917" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1917"/>
-      <c r="B1917"/>
-      <c r="C1917"/>
-      <c r="D1917"/>
-      <c r="E1917"/>
+      <c r="A1917" t="s">
+        <v>3814</v>
+      </c>
+      <c r="C1917" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E1917" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1918" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1918"/>
-      <c r="B1918"/>
-      <c r="C1918"/>
-      <c r="D1918"/>
-      <c r="E1918"/>
+      <c r="A1918" t="s">
+        <v>3815</v>
+      </c>
+      <c r="C1918" t="s">
+        <v>3816</v>
+      </c>
+      <c r="E1918" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1919" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1919"/>
-      <c r="B1919"/>
-      <c r="C1919"/>
-      <c r="D1919"/>
-      <c r="E1919"/>
+      <c r="A1919" t="s">
+        <v>3817</v>
+      </c>
+      <c r="C1919" t="s">
+        <v>3818</v>
+      </c>
+      <c r="E1919" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1920" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1920"/>
-      <c r="B1920"/>
-      <c r="C1920"/>
-      <c r="D1920"/>
-      <c r="E1920"/>
+      <c r="A1920" t="s">
+        <v>3819</v>
+      </c>
+      <c r="C1920" t="s">
+        <v>3818</v>
+      </c>
+      <c r="E1920" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1921" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1921"/>
-      <c r="B1921"/>
-      <c r="C1921"/>
-      <c r="D1921"/>
-      <c r="E1921"/>
+      <c r="A1921" t="s">
+        <v>3820</v>
+      </c>
+      <c r="C1921" t="s">
+        <v>2745</v>
+      </c>
+      <c r="E1921" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1922" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1922"/>
-      <c r="B1922"/>
-      <c r="C1922"/>
-      <c r="D1922"/>
-      <c r="E1922"/>
+      <c r="A1922" t="s">
+        <v>3821</v>
+      </c>
+      <c r="C1922" t="s">
+        <v>3484</v>
+      </c>
+      <c r="E1922" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1923" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1923"/>
-      <c r="B1923"/>
-      <c r="C1923"/>
-      <c r="D1923"/>
-      <c r="E1923"/>
+      <c r="A1923" t="s">
+        <v>3822</v>
+      </c>
+      <c r="C1923" t="s">
+        <v>3823</v>
+      </c>
+      <c r="E1923" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1924" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1924"/>
-      <c r="B1924"/>
-      <c r="C1924"/>
-      <c r="D1924"/>
-      <c r="E1924"/>
+      <c r="A1924" t="s">
+        <v>3824</v>
+      </c>
+      <c r="C1924" t="s">
+        <v>3825</v>
+      </c>
+      <c r="E1924" s="9" t="s">
+        <v>3794</v>
+      </c>
     </row>
     <row r="1925" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1925"/>
-      <c r="B1925"/>
-      <c r="C1925"/>
-      <c r="D1925"/>
-      <c r="E1925"/>
+      <c r="A1925" t="s">
+        <v>3826</v>
+      </c>
+      <c r="C1925" t="s">
+        <v>3827</v>
+      </c>
+      <c r="E1925" s="9" t="s">
+        <v>3785</v>
+      </c>
     </row>
     <row r="1926" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1926"/>
